--- a/projets/fromages/cheeseData/fromagescsv-fromagescsv.xlsx
+++ b/projets/fromages/cheeseData/fromagescsv-fromagescsv.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="664">
   <si>
     <t xml:space="preserve">departement</t>
   </si>
@@ -304,6 +304,9 @@
     <t xml:space="preserve">http://en.wikipedia.org/wiki/Bleu_d%27Auvergne</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">blue-cheese</t>
   </si>
   <si>
@@ -499,6 +502,9 @@
     <t xml:space="preserve">http://en.wikipedia.org/wiki/Brie_de_Meaux</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Fichier:Brie_01.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seine-et-Marne</t>
   </si>
   <si>
@@ -511,6 +517,9 @@
     <t xml:space="preserve">http://fr.wikipedia.org/wiki/Brie_de_Melun</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Brie_de_Melun#/media/Fichier:Wikicheese_-_Brie_de_Melun_-_20150515_-_015.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brie de Montereau</t>
   </si>
   <si>
@@ -542,6 +551,9 @@
   </si>
   <si>
     <t xml:space="preserve">http://en.wikipedia.org/wiki/Cab%C3%A9cou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Cab%C3%A9cou#/media/Fichier:Cab%C3%A9cou_de_l'Aveyron.JPG</t>
   </si>
   <si>
     <t xml:space="preserve">Charente-Maritime</t>
@@ -2013,11 +2025,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$-409]m/d/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2039,12 +2052,21 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2089,7 +2111,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2103,6 +2125,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2145,13 +2171,14 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G337"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.87"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="0" width="18.47"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="0" width="58.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="71.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2630,16 +2657,19 @@
       <c r="D27" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E27" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>90</v>
@@ -2650,16 +2680,19 @@
       <c r="D28" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E28" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>90</v>
@@ -2670,16 +2703,19 @@
       <c r="D29" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E29" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>90</v>
@@ -2690,16 +2726,19 @@
       <c r="D30" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E30" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>90</v>
@@ -2710,16 +2749,19 @@
       <c r="D31" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E31" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>90</v>
@@ -2730,16 +2772,19 @@
       <c r="D32" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E32" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>90</v>
@@ -2750,68 +2795,71 @@
       <c r="D33" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E33" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="F33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="F36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2819,50 +2867,50 @@
         <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2870,16 +2918,16 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2887,73 +2935,73 @@
         <v>29</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2961,16 +3009,16 @@
         <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2978,84 +3026,84 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>24</v>
@@ -3066,13 +3114,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>24</v>
@@ -3086,10 +3134,10 @@
         <v>25</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>24</v>
@@ -3103,10 +3151,10 @@
         <v>66</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>24</v>
@@ -3120,10 +3168,10 @@
         <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>24</v>
@@ -3137,10 +3185,10 @@
         <v>25</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>24</v>
@@ -3154,10 +3202,10 @@
         <v>61</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>60</v>
@@ -3168,22 +3216,22 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3191,10 +3239,10 @@
         <v>29</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>24</v>
@@ -3205,16 +3253,19 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>159</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>24</v>
@@ -3225,16 +3276,19 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>157</v>
+      <c r="E60" s="0" t="s">
+        <v>159</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>24</v>
@@ -3245,16 +3299,19 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" s="0" t="s">
         <v>159</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>24</v>
@@ -3268,13 +3325,16 @@
         <v>69</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>159</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>24</v>
@@ -3288,10 +3348,13 @@
         <v>25</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>164</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>24</v>
@@ -3302,13 +3365,16 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>164</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>24</v>
@@ -3322,10 +3388,13 @@
         <v>69</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>164</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>24</v>
@@ -3336,13 +3405,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>24</v>
@@ -3353,13 +3422,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>24</v>
@@ -3373,10 +3442,10 @@
         <v>7</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -3390,10 +3459,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>60</v>
@@ -3404,16 +3473,19 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>176</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>60</v>
@@ -3424,16 +3496,19 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>176</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>60</v>
@@ -3444,16 +3519,19 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>176</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>60</v>
@@ -3464,13 +3542,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>24</v>
@@ -3481,16 +3559,16 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>24</v>
@@ -3501,13 +3579,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>24</v>
@@ -3518,13 +3596,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>24</v>
@@ -3535,33 +3613,33 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>24</v>
@@ -3575,10 +3653,10 @@
         <v>66</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>24</v>
@@ -3589,13 +3667,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>24</v>
@@ -3606,16 +3684,16 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>60</v>
@@ -3626,13 +3704,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>24</v>
@@ -3646,10 +3724,10 @@
         <v>83</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>24</v>
@@ -3660,13 +3738,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>24</v>
@@ -3680,13 +3758,13 @@
         <v>69</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>24</v>
@@ -3700,10 +3778,10 @@
         <v>83</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>60</v>
@@ -3717,10 +3795,10 @@
         <v>50</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>60</v>
@@ -3731,13 +3809,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>60</v>
@@ -3751,10 +3829,10 @@
         <v>61</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>60</v>
@@ -3765,16 +3843,16 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>24</v>
@@ -3785,13 +3863,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>24</v>
@@ -3802,13 +3880,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>24</v>
@@ -3819,16 +3897,16 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>60</v>
@@ -3839,13 +3917,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>24</v>
@@ -3856,13 +3934,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>60</v>
@@ -3873,13 +3951,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>24</v>
@@ -3890,13 +3968,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>24</v>
@@ -3907,13 +3985,13 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>60</v>
@@ -3927,10 +4005,10 @@
         <v>89</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>60</v>
@@ -3944,13 +4022,13 @@
         <v>29</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>60</v>
@@ -3961,13 +4039,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>24</v>
@@ -3978,16 +4056,16 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>24</v>
@@ -4001,10 +4079,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -4015,16 +4093,16 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>24</v>
@@ -4035,16 +4113,16 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>60</v>
@@ -4055,13 +4133,13 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>24</v>
@@ -4072,16 +4150,16 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>24</v>
@@ -4092,13 +4170,13 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>24</v>
@@ -4109,16 +4187,16 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>60</v>
@@ -4129,16 +4207,16 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>60</v>
@@ -4152,10 +4230,10 @@
         <v>66</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>24</v>
@@ -4169,10 +4247,10 @@
         <v>80</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>24</v>
@@ -4183,13 +4261,13 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>24</v>
@@ -4200,13 +4278,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>24</v>
@@ -4217,13 +4295,13 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>24</v>
@@ -4237,10 +4315,10 @@
         <v>29</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>24</v>
@@ -4254,13 +4332,13 @@
         <v>17</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>24</v>
@@ -4274,13 +4352,13 @@
         <v>25</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>24</v>
@@ -4291,16 +4369,16 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>24</v>
@@ -4314,13 +4392,13 @@
         <v>12</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -4331,13 +4409,13 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>24</v>
@@ -4348,13 +4426,13 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>24</v>
@@ -4365,53 +4443,53 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4419,39 +4497,39 @@
         <v>89</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4459,19 +4537,19 @@
         <v>89</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4479,10 +4557,10 @@
         <v>89</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>24</v>
@@ -4493,13 +4571,13 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>24</v>
@@ -4510,13 +4588,13 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>24</v>
@@ -4530,44 +4608,44 @@
         <v>29</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>24</v>
@@ -4578,16 +4656,16 @@
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>24</v>
@@ -4598,19 +4676,19 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4618,13 +4696,13 @@
         <v>89</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>24</v>
@@ -4638,10 +4716,10 @@
         <v>12</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -4652,13 +4730,13 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>24</v>
@@ -4672,10 +4750,10 @@
         <v>83</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>24</v>
@@ -4689,10 +4767,10 @@
         <v>29</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>60</v>
@@ -4703,13 +4781,13 @@
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>24</v>
@@ -4720,13 +4798,13 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>24</v>
@@ -4737,13 +4815,13 @@
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>24</v>
@@ -4757,10 +4835,10 @@
         <v>61</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>24</v>
@@ -4771,13 +4849,13 @@
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>24</v>
@@ -4791,10 +4869,10 @@
         <v>29</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>24</v>
@@ -4805,13 +4883,13 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>24</v>
@@ -4825,10 +4903,10 @@
         <v>17</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>24</v>
@@ -4839,13 +4917,13 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>24</v>
@@ -4856,13 +4934,13 @@
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="C151" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>24</v>
@@ -4873,13 +4951,13 @@
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>24</v>
@@ -4890,13 +4968,13 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>24</v>
@@ -4907,13 +4985,13 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>24</v>
@@ -4927,10 +5005,10 @@
         <v>12</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>10</v>
@@ -4941,19 +5019,19 @@
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4961,10 +5039,10 @@
         <v>17</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>24</v>
@@ -4975,13 +5053,13 @@
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>24</v>
@@ -4992,13 +5070,13 @@
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>24</v>
@@ -5012,10 +5090,10 @@
         <v>50</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>60</v>
@@ -5026,16 +5104,16 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>24</v>
@@ -5046,16 +5124,16 @@
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>24</v>
@@ -5066,16 +5144,16 @@
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>24</v>
@@ -5086,16 +5164,16 @@
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>24</v>
@@ -5106,16 +5184,16 @@
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>24</v>
@@ -5129,10 +5207,10 @@
         <v>66</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>24</v>
@@ -5146,16 +5224,16 @@
         <v>12</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5163,10 +5241,10 @@
         <v>12</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>10</v>
@@ -5177,30 +5255,30 @@
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>24</v>
@@ -5214,10 +5292,10 @@
         <v>83</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>24</v>
@@ -5228,13 +5306,13 @@
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
@@ -5245,13 +5323,13 @@
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>24</v>
@@ -5265,10 +5343,10 @@
         <v>89</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>10</v>
@@ -5282,10 +5360,10 @@
         <v>86</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>10</v>
@@ -5296,13 +5374,13 @@
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>24</v>
@@ -5313,13 +5391,13 @@
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>24</v>
@@ -5333,10 +5411,10 @@
         <v>86</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>24</v>
@@ -5350,10 +5428,10 @@
         <v>66</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>24</v>
@@ -5364,16 +5442,16 @@
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>24</v>
@@ -5384,13 +5462,13 @@
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>24</v>
@@ -5404,13 +5482,13 @@
         <v>17</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>24</v>
@@ -5421,13 +5499,13 @@
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>10</v>
@@ -5438,13 +5516,13 @@
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
@@ -5458,13 +5536,13 @@
         <v>61</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>60</v>
@@ -5478,13 +5556,13 @@
         <v>50</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>60</v>
@@ -5498,13 +5576,13 @@
         <v>66</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>24</v>
@@ -5518,10 +5596,10 @@
         <v>29</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>24</v>
@@ -5532,13 +5610,13 @@
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>24</v>
@@ -5552,13 +5630,13 @@
         <v>66</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>24</v>
@@ -5569,19 +5647,19 @@
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,10 +5667,10 @@
         <v>61</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>60</v>
@@ -5606,10 +5684,10 @@
         <v>86</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>24</v>
@@ -5620,16 +5698,16 @@
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>24</v>
@@ -5640,16 +5718,16 @@
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>24</v>
@@ -5663,13 +5741,13 @@
         <v>61</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>24</v>
@@ -5680,16 +5758,16 @@
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>24</v>
@@ -5700,16 +5778,16 @@
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>24</v>
@@ -5720,13 +5798,13 @@
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>24</v>
@@ -5737,16 +5815,16 @@
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>24</v>
@@ -5757,16 +5835,16 @@
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>24</v>
@@ -5777,16 +5855,16 @@
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>24</v>
@@ -5797,16 +5875,16 @@
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>24</v>
@@ -5817,16 +5895,16 @@
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="C204" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>24</v>
@@ -5837,16 +5915,16 @@
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="D205" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>24</v>
@@ -5857,16 +5935,16 @@
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>24</v>
@@ -5877,16 +5955,16 @@
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>24</v>
@@ -5897,16 +5975,16 @@
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>24</v>
@@ -5917,13 +5995,13 @@
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>24</v>
@@ -5934,16 +6012,16 @@
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>24</v>
@@ -5957,13 +6035,13 @@
         <v>72</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>10</v>
@@ -5977,13 +6055,13 @@
         <v>12</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
@@ -5994,13 +6072,13 @@
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>10</v>
@@ -6014,13 +6092,13 @@
         <v>12</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>10</v>
@@ -6031,13 +6109,13 @@
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>24</v>
@@ -6048,13 +6126,13 @@
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>24</v>
@@ -6065,13 +6143,13 @@
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>24</v>
@@ -6082,13 +6160,13 @@
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>24</v>
@@ -6099,13 +6177,13 @@
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>24</v>
@@ -6116,13 +6194,13 @@
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>24</v>
@@ -6133,13 +6211,13 @@
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>24</v>
@@ -6150,16 +6228,16 @@
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>60</v>
@@ -6170,16 +6248,16 @@
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>60</v>
@@ -6190,16 +6268,16 @@
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="C224" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>60</v>
@@ -6210,16 +6288,16 @@
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="D225" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>60</v>
@@ -6230,16 +6308,16 @@
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>60</v>
@@ -6250,16 +6328,16 @@
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
@@ -6270,16 +6348,16 @@
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>10</v>
@@ -6290,19 +6368,19 @@
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6310,16 +6388,16 @@
         <v>29</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6327,16 +6405,16 @@
         <v>29</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6344,33 +6422,33 @@
         <v>39</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6378,44 +6456,44 @@
         <v>29</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>60</v>
@@ -6429,10 +6507,10 @@
         <v>17</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>24</v>
@@ -6443,13 +6521,13 @@
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>24</v>
@@ -6463,10 +6541,10 @@
         <v>39</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>24</v>
@@ -6477,16 +6555,16 @@
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>60</v>
@@ -6497,16 +6575,16 @@
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>60</v>
@@ -6517,16 +6595,16 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>60</v>
@@ -6537,16 +6615,16 @@
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>60</v>
@@ -6557,13 +6635,13 @@
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>24</v>
@@ -6574,13 +6652,13 @@
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>24</v>
@@ -6591,13 +6669,13 @@
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>24</v>
@@ -6608,16 +6686,16 @@
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>24</v>
@@ -6628,16 +6706,16 @@
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>24</v>
@@ -6648,16 +6726,16 @@
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>24</v>
@@ -6668,16 +6746,16 @@
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>24</v>
@@ -6688,16 +6766,16 @@
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>24</v>
@@ -6708,16 +6786,16 @@
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>24</v>
@@ -6728,16 +6806,16 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>24</v>
@@ -6751,13 +6829,13 @@
         <v>57</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>60</v>
@@ -6768,19 +6846,19 @@
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6788,13 +6866,13 @@
         <v>29</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>24</v>
@@ -6805,13 +6883,13 @@
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>24</v>
@@ -6822,13 +6900,13 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>10</v>
@@ -6839,19 +6917,19 @@
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6859,13 +6937,13 @@
         <v>29</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>24</v>
@@ -6876,13 +6954,13 @@
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>10</v>
@@ -6896,13 +6974,13 @@
         <v>50</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>60</v>
@@ -6913,16 +6991,16 @@
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>60</v>
@@ -6933,13 +7011,13 @@
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>60</v>
@@ -6950,16 +7028,16 @@
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>60</v>
@@ -6970,33 +7048,33 @@
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>24</v>
@@ -7007,13 +7085,13 @@
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>60</v>
@@ -7024,13 +7102,13 @@
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>24</v>
@@ -7044,10 +7122,10 @@
         <v>66</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>24</v>
@@ -7058,13 +7136,13 @@
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>24</v>
@@ -7075,22 +7153,22 @@
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7098,10 +7176,10 @@
         <v>89</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>10</v>
@@ -7112,22 +7190,22 @@
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7135,13 +7213,13 @@
         <v>12</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>24</v>
@@ -7152,13 +7230,13 @@
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>24</v>
@@ -7172,10 +7250,10 @@
         <v>25</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>24</v>
@@ -7186,13 +7264,13 @@
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>24</v>
@@ -7206,10 +7284,10 @@
         <v>39</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>24</v>
@@ -7223,13 +7301,13 @@
         <v>89</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>24</v>
@@ -7240,16 +7318,16 @@
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>24</v>
@@ -7263,13 +7341,13 @@
         <v>57</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>60</v>
@@ -7280,16 +7358,16 @@
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>60</v>
@@ -7300,16 +7378,16 @@
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>60</v>
@@ -7320,16 +7398,16 @@
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>60</v>
@@ -7340,16 +7418,16 @@
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>24</v>
@@ -7360,13 +7438,13 @@
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>60</v>
@@ -7377,16 +7455,16 @@
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>60</v>
@@ -7397,19 +7475,19 @@
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7417,10 +7495,10 @@
         <v>25</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>24</v>
@@ -7434,10 +7512,10 @@
         <v>69</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>24</v>
@@ -7448,19 +7526,19 @@
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7468,10 +7546,10 @@
         <v>25</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>24</v>
@@ -7485,10 +7563,10 @@
         <v>66</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>24</v>
@@ -7499,13 +7577,13 @@
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>60</v>
@@ -7516,13 +7594,13 @@
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>60</v>
@@ -7536,27 +7614,27 @@
         <v>29</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>24</v>
@@ -7570,16 +7648,16 @@
         <v>29</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7587,10 +7665,10 @@
         <v>66</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>24</v>
@@ -7604,10 +7682,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>24</v>
@@ -7621,10 +7699,10 @@
         <v>29</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>24</v>
@@ -7638,10 +7716,10 @@
         <v>39</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>24</v>
@@ -7652,13 +7730,13 @@
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>24</v>
@@ -7669,13 +7747,13 @@
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>24</v>
@@ -7686,13 +7764,13 @@
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>24</v>
@@ -7706,10 +7784,10 @@
         <v>12</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>10</v>
@@ -7720,13 +7798,13 @@
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>24</v>
@@ -7740,10 +7818,10 @@
         <v>29</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>24</v>
@@ -7757,10 +7835,10 @@
         <v>29</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>24</v>
@@ -7771,13 +7849,13 @@
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>24</v>
@@ -7788,13 +7866,13 @@
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>24</v>
@@ -7808,13 +7886,13 @@
         <v>29</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>24</v>
@@ -7825,16 +7903,16 @@
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>24</v>
@@ -7848,13 +7926,13 @@
         <v>72</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>24</v>
@@ -7865,16 +7943,16 @@
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>24</v>
@@ -7888,13 +7966,13 @@
         <v>86</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>24</v>
@@ -7908,13 +7986,13 @@
         <v>12</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>24</v>
@@ -7928,16 +8006,16 @@
         <v>29</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7945,10 +8023,10 @@
         <v>57</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>60</v>
@@ -7959,13 +8037,13 @@
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>24</v>
@@ -7976,30 +8054,30 @@
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>24</v>
@@ -8010,13 +8088,13 @@
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>24</v>
@@ -8030,10 +8108,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>24</v>
@@ -8044,13 +8122,13 @@
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>24</v>
@@ -8061,13 +8139,13 @@
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>10</v>
@@ -8078,13 +8156,13 @@
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>60</v>
@@ -8098,10 +8176,10 @@
         <v>29</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>24</v>
@@ -8112,16 +8190,16 @@
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>60</v>
@@ -8132,16 +8210,16 @@
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>60</v>
@@ -8152,16 +8230,16 @@
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>60</v>
@@ -8175,13 +8253,13 @@
         <v>57</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>60</v>
@@ -8192,16 +8270,16 @@
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>20</v>
@@ -8212,13 +8290,13 @@
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>24</v>
@@ -8229,13 +8307,13 @@
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>24</v>
@@ -8246,13 +8324,13 @@
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>24</v>
@@ -8277,6 +8355,15 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E27" r:id="rId1" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E28" r:id="rId2" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E29" r:id="rId3" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E30" r:id="rId4" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E31" r:id="rId5" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E32" r:id="rId6" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E33" r:id="rId7" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8284,6 +8371,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
--- a/projets/fromages/cheeseData/fromagescsv-fromagescsv.xlsx
+++ b/projets/fromages/cheeseData/fromagescsv-fromagescsv.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="661">
   <si>
     <t xml:space="preserve">departement</t>
   </si>
@@ -304,9 +304,6 @@
     <t xml:space="preserve">http://en.wikipedia.org/wiki/Bleu_d%27Auvergne</t>
   </si>
   <si>
-    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">blue-cheese</t>
   </si>
   <si>
@@ -502,9 +499,6 @@
     <t xml:space="preserve">http://en.wikipedia.org/wiki/Brie_de_Meaux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Fichier:Brie_01.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seine-et-Marne</t>
   </si>
   <si>
@@ -517,9 +511,6 @@
     <t xml:space="preserve">http://fr.wikipedia.org/wiki/Brie_de_Melun</t>
   </si>
   <si>
-    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Brie_de_Melun#/media/Fichier:Wikicheese_-_Brie_de_Melun_-_20150515_-_015.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brie de Montereau</t>
   </si>
   <si>
@@ -553,9 +544,6 @@
     <t xml:space="preserve">http://en.wikipedia.org/wiki/Cab%C3%A9cou</t>
   </si>
   <si>
-    <t xml:space="preserve">https://fr.wikipedia.org/wiki/Cab%C3%A9cou#/media/Fichier:Cab%C3%A9cou_de_l'Aveyron.JPG</t>
-  </si>
-  <si>
     <t xml:space="preserve">Charente-Maritime</t>
   </si>
   <si>
@@ -665,6 +653,9 @@
   </si>
   <si>
     <t xml:space="preserve">http://fr.wikipedia.org/wiki/Charolais_%28fromage%29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7f/Fromage_charolais.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Loire</t>
@@ -2657,19 +2648,16 @@
       <c r="D27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>90</v>
@@ -2680,19 +2668,16 @@
       <c r="D28" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>90</v>
@@ -2703,19 +2688,16 @@
       <c r="D29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>90</v>
@@ -2726,19 +2708,16 @@
       <c r="D30" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>90</v>
@@ -2749,19 +2728,16 @@
       <c r="D31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="F31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>90</v>
@@ -2772,19 +2748,16 @@
       <c r="D32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>90</v>
@@ -2795,71 +2768,68 @@
       <c r="D33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F35" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F36" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2867,50 +2837,50 @@
         <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="F37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2918,16 +2888,16 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2935,73 +2905,73 @@
         <v>29</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="F41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3009,16 +2979,16 @@
         <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3026,84 +2996,84 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="F46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="F48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="F49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>24</v>
@@ -3114,13 +3084,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>24</v>
@@ -3134,10 +3104,10 @@
         <v>25</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>24</v>
@@ -3151,10 +3121,10 @@
         <v>66</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>24</v>
@@ -3168,10 +3138,10 @@
         <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>24</v>
@@ -3185,10 +3155,10 @@
         <v>25</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>24</v>
@@ -3202,10 +3172,10 @@
         <v>61</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>60</v>
@@ -3216,22 +3186,22 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="F57" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3239,10 +3209,10 @@
         <v>29</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>24</v>
@@ -3253,19 +3223,16 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E59" s="0" t="s">
-        <v>159</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>24</v>
@@ -3276,19 +3243,16 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E60" s="0" t="s">
-        <v>159</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>24</v>
@@ -3299,19 +3263,16 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E61" s="0" t="s">
-        <v>159</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>24</v>
@@ -3325,16 +3286,13 @@
         <v>69</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E62" s="0" t="s">
-        <v>159</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>24</v>
@@ -3348,13 +3306,10 @@
         <v>25</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E63" s="0" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>24</v>
@@ -3365,16 +3320,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E64" s="0" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>24</v>
@@ -3388,13 +3340,10 @@
         <v>69</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E65" s="0" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>24</v>
@@ -3405,13 +3354,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>24</v>
@@ -3422,13 +3371,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>24</v>
@@ -3442,10 +3391,10 @@
         <v>7</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -3459,10 +3408,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>60</v>
@@ -3473,19 +3422,16 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>60</v>
@@ -3496,19 +3442,16 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E71" s="0" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>60</v>
@@ -3519,19 +3462,16 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E72" s="0" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>60</v>
@@ -3542,13 +3482,13 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>24</v>
@@ -3559,16 +3499,16 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>24</v>
@@ -3579,13 +3519,13 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>24</v>
@@ -3596,13 +3536,13 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>24</v>
@@ -3613,33 +3553,33 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>24</v>
@@ -3653,10 +3593,10 @@
         <v>66</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>24</v>
@@ -3667,13 +3607,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>24</v>
@@ -3684,16 +3624,16 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>60</v>
@@ -3704,13 +3644,13 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>24</v>
@@ -3724,10 +3664,10 @@
         <v>83</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>24</v>
@@ -3738,13 +3678,13 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>24</v>
@@ -3758,13 +3698,13 @@
         <v>69</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>24</v>
@@ -3778,10 +3718,13 @@
         <v>83</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>60</v>
@@ -3795,10 +3738,13 @@
         <v>50</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>60</v>
@@ -3809,13 +3755,16 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>60</v>
@@ -3829,10 +3778,13 @@
         <v>61</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>60</v>
@@ -3843,16 +3795,16 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>24</v>
@@ -3863,13 +3815,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>24</v>
@@ -3880,13 +3832,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>24</v>
@@ -3897,16 +3849,16 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>60</v>
@@ -3917,13 +3869,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>24</v>
@@ -3934,13 +3886,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>60</v>
@@ -3951,13 +3903,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>24</v>
@@ -3968,13 +3920,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>24</v>
@@ -3985,13 +3937,13 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>60</v>
@@ -4005,10 +3957,10 @@
         <v>89</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>60</v>
@@ -4022,13 +3974,13 @@
         <v>29</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>60</v>
@@ -4039,13 +3991,13 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>24</v>
@@ -4056,16 +4008,16 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>24</v>
@@ -4079,10 +4031,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -4093,16 +4045,16 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>24</v>
@@ -4113,16 +4065,16 @@
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>60</v>
@@ -4133,13 +4085,13 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>24</v>
@@ -4150,16 +4102,16 @@
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>24</v>
@@ -4170,13 +4122,13 @@
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>24</v>
@@ -4187,16 +4139,16 @@
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>60</v>
@@ -4207,16 +4159,16 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>60</v>
@@ -4230,10 +4182,10 @@
         <v>66</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>24</v>
@@ -4247,10 +4199,10 @@
         <v>80</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>24</v>
@@ -4261,13 +4213,13 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>24</v>
@@ -4278,13 +4230,13 @@
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>24</v>
@@ -4295,13 +4247,13 @@
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>24</v>
@@ -4315,10 +4267,10 @@
         <v>29</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>24</v>
@@ -4332,13 +4284,13 @@
         <v>17</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>24</v>
@@ -4352,13 +4304,13 @@
         <v>25</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>24</v>
@@ -4369,16 +4321,16 @@
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>24</v>
@@ -4392,13 +4344,13 @@
         <v>12</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -4409,13 +4361,13 @@
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>24</v>
@@ -4426,13 +4378,13 @@
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>24</v>
@@ -4443,53 +4395,53 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4497,39 +4449,39 @@
         <v>89</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4537,19 +4489,19 @@
         <v>89</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4557,10 +4509,10 @@
         <v>89</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>24</v>
@@ -4571,13 +4523,13 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>24</v>
@@ -4588,13 +4540,13 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>24</v>
@@ -4608,44 +4560,44 @@
         <v>29</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>24</v>
@@ -4656,16 +4608,16 @@
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>24</v>
@@ -4676,19 +4628,19 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4696,13 +4648,13 @@
         <v>89</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>24</v>
@@ -4716,10 +4668,10 @@
         <v>12</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -4730,13 +4682,13 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>24</v>
@@ -4750,10 +4702,10 @@
         <v>83</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>24</v>
@@ -4767,10 +4719,10 @@
         <v>29</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>60</v>
@@ -4781,13 +4733,13 @@
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>24</v>
@@ -4798,13 +4750,13 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>24</v>
@@ -4815,13 +4767,13 @@
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>24</v>
@@ -4835,10 +4787,10 @@
         <v>61</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>24</v>
@@ -4849,13 +4801,13 @@
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>24</v>
@@ -4869,10 +4821,10 @@
         <v>29</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>24</v>
@@ -4883,13 +4835,13 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>24</v>
@@ -4903,10 +4855,10 @@
         <v>17</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>24</v>
@@ -4917,13 +4869,13 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>24</v>
@@ -4934,13 +4886,13 @@
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>24</v>
@@ -4951,13 +4903,13 @@
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>24</v>
@@ -4968,13 +4920,13 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>24</v>
@@ -4985,13 +4937,13 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>24</v>
@@ -5005,10 +4957,10 @@
         <v>12</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>10</v>
@@ -5019,19 +4971,19 @@
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5039,10 +4991,10 @@
         <v>17</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>24</v>
@@ -5053,13 +5005,13 @@
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>24</v>
@@ -5070,13 +5022,13 @@
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>24</v>
@@ -5090,10 +5042,10 @@
         <v>50</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>60</v>
@@ -5104,16 +5056,16 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>24</v>
@@ -5124,16 +5076,16 @@
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>24</v>
@@ -5144,16 +5096,16 @@
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>24</v>
@@ -5164,16 +5116,16 @@
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>24</v>
@@ -5184,16 +5136,16 @@
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>24</v>
@@ -5207,10 +5159,10 @@
         <v>66</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>24</v>
@@ -5224,16 +5176,16 @@
         <v>12</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5241,10 +5193,10 @@
         <v>12</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>10</v>
@@ -5255,30 +5207,30 @@
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>24</v>
@@ -5292,10 +5244,10 @@
         <v>83</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>24</v>
@@ -5306,13 +5258,13 @@
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
@@ -5323,13 +5275,13 @@
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>24</v>
@@ -5343,10 +5295,10 @@
         <v>89</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>10</v>
@@ -5360,10 +5312,10 @@
         <v>86</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>10</v>
@@ -5374,13 +5326,13 @@
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>24</v>
@@ -5391,13 +5343,13 @@
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>24</v>
@@ -5411,10 +5363,10 @@
         <v>86</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>24</v>
@@ -5428,10 +5380,10 @@
         <v>66</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>24</v>
@@ -5442,16 +5394,16 @@
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>24</v>
@@ -5462,13 +5414,13 @@
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>24</v>
@@ -5482,13 +5434,13 @@
         <v>17</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>24</v>
@@ -5499,13 +5451,13 @@
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>10</v>
@@ -5516,13 +5468,13 @@
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
@@ -5536,13 +5488,13 @@
         <v>61</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>60</v>
@@ -5556,13 +5508,13 @@
         <v>50</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>60</v>
@@ -5576,13 +5528,13 @@
         <v>66</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>24</v>
@@ -5596,10 +5548,10 @@
         <v>29</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>24</v>
@@ -5610,13 +5562,13 @@
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>24</v>
@@ -5630,13 +5582,13 @@
         <v>66</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>24</v>
@@ -5647,19 +5599,19 @@
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5667,10 +5619,10 @@
         <v>61</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>60</v>
@@ -5684,10 +5636,10 @@
         <v>86</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>24</v>
@@ -5698,16 +5650,16 @@
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>24</v>
@@ -5718,16 +5670,16 @@
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>24</v>
@@ -5741,13 +5693,13 @@
         <v>61</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>24</v>
@@ -5758,16 +5710,16 @@
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>24</v>
@@ -5778,16 +5730,16 @@
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>24</v>
@@ -5798,13 +5750,13 @@
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>24</v>
@@ -5815,16 +5767,16 @@
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D200" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>24</v>
@@ -5835,16 +5787,16 @@
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>24</v>
@@ -5855,16 +5807,16 @@
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>24</v>
@@ -5875,16 +5827,16 @@
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>24</v>
@@ -5895,16 +5847,16 @@
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>24</v>
@@ -5915,16 +5867,16 @@
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>24</v>
@@ -5935,16 +5887,16 @@
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>24</v>
@@ -5955,16 +5907,16 @@
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>24</v>
@@ -5975,16 +5927,16 @@
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>24</v>
@@ -5995,13 +5947,13 @@
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>24</v>
@@ -6012,16 +5964,16 @@
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>24</v>
@@ -6035,13 +5987,13 @@
         <v>72</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>10</v>
@@ -6055,13 +6007,13 @@
         <v>12</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
@@ -6072,13 +6024,13 @@
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>10</v>
@@ -6092,13 +6044,13 @@
         <v>12</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>10</v>
@@ -6109,13 +6061,13 @@
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>24</v>
@@ -6126,13 +6078,13 @@
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>24</v>
@@ -6143,13 +6095,13 @@
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>24</v>
@@ -6160,13 +6112,13 @@
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>24</v>
@@ -6177,13 +6129,13 @@
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>24</v>
@@ -6194,13 +6146,13 @@
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>24</v>
@@ -6211,13 +6163,13 @@
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>24</v>
@@ -6228,16 +6180,16 @@
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D222" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>60</v>
@@ -6248,16 +6200,16 @@
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>60</v>
@@ -6268,16 +6220,16 @@
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>60</v>
@@ -6288,16 +6240,16 @@
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>60</v>
@@ -6308,16 +6260,16 @@
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>60</v>
@@ -6328,16 +6280,16 @@
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
@@ -6348,16 +6300,16 @@
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>10</v>
@@ -6368,19 +6320,19 @@
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6388,16 +6340,16 @@
         <v>29</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6405,16 +6357,16 @@
         <v>29</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6422,33 +6374,33 @@
         <v>39</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6456,44 +6408,44 @@
         <v>29</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>60</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>60</v>
@@ -6507,10 +6459,10 @@
         <v>17</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>24</v>
@@ -6521,13 +6473,13 @@
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>24</v>
@@ -6541,10 +6493,10 @@
         <v>39</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>24</v>
@@ -6555,16 +6507,16 @@
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>60</v>
@@ -6575,16 +6527,16 @@
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>60</v>
@@ -6595,16 +6547,16 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>60</v>
@@ -6615,16 +6567,16 @@
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>60</v>
@@ -6635,13 +6587,13 @@
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>24</v>
@@ -6652,13 +6604,13 @@
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>24</v>
@@ -6669,13 +6621,13 @@
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>24</v>
@@ -6686,16 +6638,16 @@
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>24</v>
@@ -6706,16 +6658,16 @@
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>24</v>
@@ -6726,16 +6678,16 @@
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>24</v>
@@ -6746,16 +6698,16 @@
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>24</v>
@@ -6766,16 +6718,16 @@
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>24</v>
@@ -6786,16 +6738,16 @@
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>24</v>
@@ -6806,16 +6758,16 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>24</v>
@@ -6829,13 +6781,13 @@
         <v>57</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>60</v>
@@ -6846,19 +6798,19 @@
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6866,13 +6818,13 @@
         <v>29</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>24</v>
@@ -6883,13 +6835,13 @@
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>24</v>
@@ -6900,13 +6852,13 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>10</v>
@@ -6917,19 +6869,19 @@
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6937,13 +6889,13 @@
         <v>29</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>24</v>
@@ -6954,13 +6906,13 @@
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>10</v>
@@ -6974,13 +6926,13 @@
         <v>50</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>60</v>
@@ -6991,16 +6943,16 @@
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>60</v>
@@ -7011,13 +6963,13 @@
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>60</v>
@@ -7028,16 +6980,16 @@
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>60</v>
@@ -7048,33 +7000,33 @@
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>24</v>
@@ -7085,13 +7037,13 @@
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>60</v>
@@ -7102,13 +7054,13 @@
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>24</v>
@@ -7122,10 +7074,10 @@
         <v>66</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>24</v>
@@ -7136,13 +7088,13 @@
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>24</v>
@@ -7153,22 +7105,22 @@
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7176,10 +7128,10 @@
         <v>89</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>10</v>
@@ -7190,22 +7142,22 @@
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7213,13 +7165,13 @@
         <v>12</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>24</v>
@@ -7230,13 +7182,13 @@
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>24</v>
@@ -7250,10 +7202,10 @@
         <v>25</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>24</v>
@@ -7264,13 +7216,13 @@
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>24</v>
@@ -7284,10 +7236,10 @@
         <v>39</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>24</v>
@@ -7301,13 +7253,13 @@
         <v>89</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>24</v>
@@ -7318,16 +7270,16 @@
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>24</v>
@@ -7341,13 +7293,13 @@
         <v>57</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>60</v>
@@ -7358,16 +7310,16 @@
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>60</v>
@@ -7378,16 +7330,16 @@
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>60</v>
@@ -7398,16 +7350,16 @@
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>60</v>
@@ -7418,16 +7370,16 @@
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>24</v>
@@ -7438,13 +7390,13 @@
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>60</v>
@@ -7455,16 +7407,16 @@
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>60</v>
@@ -7475,19 +7427,19 @@
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7495,10 +7447,10 @@
         <v>25</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>24</v>
@@ -7512,10 +7464,10 @@
         <v>69</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>24</v>
@@ -7526,19 +7478,19 @@
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7546,10 +7498,10 @@
         <v>25</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>24</v>
@@ -7563,10 +7515,10 @@
         <v>66</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>24</v>
@@ -7577,13 +7529,13 @@
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>60</v>
@@ -7594,13 +7546,13 @@
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>60</v>
@@ -7614,27 +7566,27 @@
         <v>29</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>24</v>
@@ -7648,16 +7600,16 @@
         <v>29</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7665,10 +7617,10 @@
         <v>66</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>24</v>
@@ -7682,10 +7634,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>24</v>
@@ -7699,10 +7651,10 @@
         <v>29</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>24</v>
@@ -7716,10 +7668,10 @@
         <v>39</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>24</v>
@@ -7730,13 +7682,13 @@
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>24</v>
@@ -7747,13 +7699,13 @@
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>24</v>
@@ -7764,13 +7716,13 @@
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>24</v>
@@ -7784,10 +7736,10 @@
         <v>12</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>10</v>
@@ -7798,13 +7750,13 @@
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>24</v>
@@ -7818,10 +7770,10 @@
         <v>29</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>24</v>
@@ -7835,10 +7787,10 @@
         <v>29</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>24</v>
@@ -7849,13 +7801,13 @@
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>24</v>
@@ -7866,13 +7818,13 @@
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>24</v>
@@ -7886,13 +7838,13 @@
         <v>29</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>24</v>
@@ -7903,16 +7855,16 @@
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>24</v>
@@ -7926,13 +7878,13 @@
         <v>72</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>24</v>
@@ -7943,16 +7895,16 @@
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>24</v>
@@ -7966,13 +7918,13 @@
         <v>86</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>24</v>
@@ -7986,13 +7938,13 @@
         <v>12</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>24</v>
@@ -8006,16 +7958,16 @@
         <v>29</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G319" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8023,10 +7975,10 @@
         <v>57</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>60</v>
@@ -8037,13 +7989,13 @@
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>24</v>
@@ -8054,30 +8006,30 @@
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G322" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>24</v>
@@ -8088,13 +8040,13 @@
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>24</v>
@@ -8108,10 +8060,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>24</v>
@@ -8122,13 +8074,13 @@
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>24</v>
@@ -8139,13 +8091,13 @@
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>10</v>
@@ -8156,13 +8108,13 @@
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>60</v>
@@ -8176,10 +8128,10 @@
         <v>29</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>24</v>
@@ -8190,16 +8142,16 @@
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>60</v>
@@ -8210,16 +8162,16 @@
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>60</v>
@@ -8230,16 +8182,16 @@
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>60</v>
@@ -8253,13 +8205,13 @@
         <v>57</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>60</v>
@@ -8270,16 +8222,16 @@
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>20</v>
@@ -8290,13 +8242,13 @@
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>24</v>
@@ -8307,13 +8259,13 @@
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>24</v>
@@ -8324,13 +8276,13 @@
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>24</v>
@@ -8356,13 +8308,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E27" r:id="rId1" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
-    <hyperlink ref="E28" r:id="rId2" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
-    <hyperlink ref="E29" r:id="rId3" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
-    <hyperlink ref="E30" r:id="rId4" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
-    <hyperlink ref="E31" r:id="rId5" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
-    <hyperlink ref="E32" r:id="rId6" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
-    <hyperlink ref="E33" r:id="rId7" location="/media/Fichier:Bleu_d'Auvergne_01.jpg" display="https://fr.wikipedia.org/wiki/Bleu_d'Auvergne#/media/Fichier:Bleu_d'Auvergne_01.jpg"/>
+    <hyperlink ref="E86" r:id="rId1" display="https://upload.wikimedia.org/wikipedia/commons/7/7f/Fromage_charolais.jpg"/>
+    <hyperlink ref="E87" r:id="rId2" display="https://upload.wikimedia.org/wikipedia/commons/7/7f/Fromage_charolais.jpg"/>
+    <hyperlink ref="E88" r:id="rId3" display="https://upload.wikimedia.org/wikipedia/commons/7/7f/Fromage_charolais.jpg"/>
+    <hyperlink ref="E89" r:id="rId4" display="https://upload.wikimedia.org/wikipedia/commons/7/7f/Fromage_charolais.jpg"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8371,6 +8320,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>